--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2013/RHODE_ISLAND_2013.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2013/RHODE_ISLAND_2013.xlsx
@@ -1075,7 +1075,7 @@
         <v>21</v>
       </c>
       <c r="D40">
-        <v>0.09905660377358499</v>
+        <v>0.09905660377358501</v>
       </c>
     </row>
     <row r="41">
